--- a/Assignment 1 - Test cases.xlsx
+++ b/Assignment 1 - Test cases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\Option 1\Test_automation_Option 1\Test_automation_Option 1\test_automation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IT3040_Assignment1_IT23212190\IT3040_Assignment1_IT23212190\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02121B89-E3DB-4032-8CF4-2C2976BCAEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D21EC7A-577B-4F7B-9BA5-764FBEA1ED2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Test Case ID</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="253">
+  <si>
+    <t>TC  ID</t>
   </si>
   <si>
     <t>Input length type</t>
@@ -34,17 +34,807 @@
     <t>Expected output</t>
   </si>
   <si>
-    <t>Actual output</t>
+    <t>Actual Output</t>
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Singlish input types covered</t>
+  </si>
+  <si>
+    <t>Evidence or rationale for the input type covered</t>
+  </si>
+  <si>
+    <t>TC_001</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>mama yanne heta oyata kiyannam</t>
+  </si>
+  <si>
+    <t>මම යන්නෙ හෙට ඔයාට කියන්නම්</t>
+  </si>
+  <si>
+    <t>මම යන්නේ හෙට ඔයාට කියන්නම්</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>Romanization / Spelling Variants</t>
+  </si>
+  <si>
+    <t>Evidence: Input uses informal or non-standard Singlish spellings.</t>
+  </si>
+  <si>
+    <t>TC_002</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>hari ehem karamu</t>
+  </si>
+  <si>
+    <t>හරි එහෙම කරමු</t>
+  </si>
+  <si>
+    <t>හරි එහෙම් කරමු</t>
+  </si>
+  <si>
+    <t>Responses</t>
+  </si>
+  <si>
+    <t>Evidence: Input represents a reply or acknowledgement.</t>
+  </si>
+  <si>
+    <t>TC_003</t>
+  </si>
+  <si>
+    <t>mage NIC eka hoyaganna one</t>
+  </si>
+  <si>
+    <t>මගේ NIC එක හොයාගන්න ඕනේ</t>
+  </si>
+  <si>
+    <t>මගේ NIC ඒක හොයාගන්න ඕනේ</t>
+  </si>
+  <si>
+    <t>English Abbreviations/Acronyms</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains abbreviations or acronyms.</t>
+  </si>
+  <si>
+    <t>TC_004</t>
+  </si>
+  <si>
+    <t>good morning ayye</t>
+  </si>
+  <si>
+    <t>ගුඩ් මෝර්නින් අයියේ</t>
+  </si>
+  <si>
+    <t>good morning අයියෙ</t>
+  </si>
+  <si>
+    <t>Greetings</t>
+  </si>
+  <si>
+    <t>Evidence: Input uses a greeting phrase.</t>
+  </si>
+  <si>
+    <t>TC_005</t>
+  </si>
+  <si>
+    <t>tikaa tikak kanna</t>
+  </si>
+  <si>
+    <t>ටිකක් ටිකක් කන්න</t>
+  </si>
+  <si>
+    <t>ටික ටිකක් කන්න</t>
+  </si>
+  <si>
+    <t>TC_006</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mokadddha?? meka	</t>
+  </si>
+  <si>
+    <t>මොකද්ද?? මේක</t>
+  </si>
+  <si>
+    <t>මොකදද?? මේක</t>
+  </si>
+  <si>
+    <t>Inputs with Punctuation Marks</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains punctuation marks.</t>
+  </si>
+  <si>
+    <t>bluetooth on කරපන්</t>
+  </si>
+  <si>
+    <t>English Digital Terms in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains digital or technology-related terms.</t>
+  </si>
+  <si>
+    <t>TC_007</t>
+  </si>
+  <si>
+    <t>doc eka upload kalaa</t>
+  </si>
+  <si>
+    <t>doc එක upload කළා</t>
+  </si>
+  <si>
+    <t>ඩොක් එක upload කළා</t>
+  </si>
+  <si>
+    <t>English Clipped Forms in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Input mixes clipped English terms with Singlish.</t>
+  </si>
+  <si>
+    <t>TC_008</t>
+  </si>
+  <si>
+    <t>mmamaheta mamalaage gedharayanawa</t>
+  </si>
+  <si>
+    <t>මම හෙට මාමලාගෙ ගෙදර යනවා</t>
+  </si>
+  <si>
+    <t>මමමහෙට මාමලාගේ ගෙදරයනවා</t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>apipansalatayannnahithninnawa</t>
+  </si>
+  <si>
+    <t>අපි පන්සලට යන්න හිතන් ඉන්නවා</t>
+  </si>
+  <si>
+    <t>අපි පන්සලට යන්න හිත්නින්නවා</t>
+  </si>
+  <si>
+    <t>TC_010</t>
+  </si>
+  <si>
+    <t>mata    pahala gedharata  yanna ooneee</t>
+  </si>
+  <si>
+    <t>මට පහල ගෙදරට යන්න ඕනෙ</t>
+  </si>
+  <si>
+    <t>මට පහල ගෙදරට යන්න ඕනේ</t>
+  </si>
+  <si>
+    <t>TC_011</t>
+  </si>
+  <si>
+    <t>mama adha kaeema kaeevee naethi nisaa bada ridhenavaa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">මම අද කෑම කෑවේ\n නැති නිසා බඩ රිදෙනවා </t>
+  </si>
+  <si>
+    <t>මම අද කෑම කෑවේ නැති නිසා බඩ රිදෙනවා</t>
+  </si>
+  <si>
+    <t>TC_012</t>
+  </si>
+  <si>
+    <t>ee machaang ee kaeema eka patta rasayineee</t>
+  </si>
+  <si>
+    <t>ඒ මචාන්ග  ඒ කෑම එක පට්ට රසයිනේ</t>
+  </si>
+  <si>
+    <t>ඊ මචාන් ඊ කෑම එක පට්ට රසයිනේඒ</t>
+  </si>
+  <si>
+    <t>Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains slang or informal chat phrasing.</t>
+  </si>
+  <si>
+    <t>TC_013</t>
+  </si>
+  <si>
+    <t>adoo ban arayaa kavudha</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> අඩෝඕ බන් අරයා කවුද</t>
+  </si>
+  <si>
+    <t>අඩෝ බන් අරයා කවුද</t>
+  </si>
+  <si>
+    <t>TC_014</t>
+  </si>
+  <si>
+    <t>apizoommeetingekatayanavaaheta</t>
+  </si>
+  <si>
+    <t>අපි zoom meeting එකට යනවා හෙට</t>
+  </si>
+  <si>
+    <t>අපිසොඔම්මේටින්ග්එකටයනවාඅහේට</t>
+  </si>
+  <si>
+    <t>Platform/App Names in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Input includes a platform or app name.</t>
+  </si>
+  <si>
+    <t>TC_015</t>
+  </si>
+  <si>
+    <t>mama FB eke status upload karala thiyenawa</t>
+  </si>
+  <si>
+    <t>මම FB එකේ status upload කරලා තියෙනවා</t>
+  </si>
+  <si>
+    <t>මම FB ඒකේ status upload කරලා තියෙනවා</t>
+  </si>
+  <si>
+    <t>TC_016</t>
+  </si>
+  <si>
+    <t>oyaagebaappaahetameheeenavadha</t>
+  </si>
+  <si>
+    <t>ඔයාගෙ බාප්පා හෙට මෙහේ එනවද</t>
+  </si>
+  <si>
+    <t>ඔයාගෙබඅප්පහෙටමඑහෙනවද</t>
+  </si>
+  <si>
+    <t>TC_017</t>
+  </si>
+  <si>
+    <t>eyi bro oyaage vaedeth karala mata diipan'i</t>
+  </si>
+  <si>
+    <t>ඒයි bro ඔයාගෙ වැඩෙත් කරල මට දීපන්</t>
+  </si>
+  <si>
+    <t>ඇයි bro ඔයාගේ වැඩේත් කරලා මට දියපන්යි</t>
+  </si>
+  <si>
+    <t>TC_018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S </t>
+  </si>
+  <si>
+    <t>rs 4500 wagei wenawa</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> rs 4500 වගේ වෙනවා</t>
+  </si>
+  <si>
+    <t>රුස් 4500 වගේයි වෙනවා</t>
+  </si>
+  <si>
+    <t>Inputs with Currency</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains a currency notation or amount.</t>
+  </si>
+  <si>
+    <t>TC_019</t>
+  </si>
+  <si>
+    <t>meeting eka 8:45am</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> meeting එක 8:45am</t>
+  </si>
+  <si>
+    <t>meeting එක 8:45ම්</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains a time expression.</t>
+  </si>
+  <si>
+    <t>TC_020</t>
+  </si>
+  <si>
+    <t>mata kalin oyaa ehe yanna epaa</t>
+  </si>
+  <si>
+    <t>මට කලින් ඔය එහෙ යන්න එපා</t>
+  </si>
+  <si>
+    <t>මට කලින් ඔයා එහේ යන්න එපා</t>
+  </si>
+  <si>
+    <t>TC_021</t>
+  </si>
+  <si>
+    <t>mata  iye eka boruvak kiyalaa therunaa</t>
+  </si>
+  <si>
+    <t>මට  ඊයේ එක බොරුවක් කියලා තේරුනා</t>
+  </si>
+  <si>
+    <t>මට ඊයේ ඒක බොරුවක් කියලා තේරුනා</t>
+  </si>
+  <si>
+    <t>TC_022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S			</t>
+  </si>
+  <si>
+    <t>km 5k duwa</t>
+  </si>
+  <si>
+    <t>km 5ක් දිව්වා</t>
+  </si>
+  <si>
+    <t>km 5ක් දුවා</t>
+  </si>
+  <si>
+    <t>Unit of Measurements</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains measurement units.</t>
+  </si>
+  <si>
+    <t>TC_023</t>
+  </si>
+  <si>
+    <t>idk mokakda une</t>
+  </si>
+  <si>
+    <t>idk මොකක්ද උනේ</t>
+  </si>
+  <si>
+    <t>ඉඳක් මොකක්ද වුණේ</t>
+  </si>
+  <si>
+    <t>TC_024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mama books 3 k gattta	</t>
+  </si>
+  <si>
+    <t>මම books 3ක් ගත්තා</t>
+  </si>
+  <si>
+    <t>මම books 3 ක් ගත්තා</t>
+  </si>
+  <si>
+    <t>Inputs with Numbers and Numeric Suffixes</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains numbers or numeric suffixes.</t>
+  </si>
+  <si>
+    <t>TC_025</t>
+  </si>
+  <si>
+    <t>ane ehema wanna epa   😭</t>
+  </si>
+  <si>
+    <t>අනේ එහෙම වෙන්න එපා 😭</t>
+  </si>
+  <si>
+    <t>අනේ එහෙම වන්න එපා 😭</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Evidence: Input contains emoji characters mixed with Singlish text.</t>
+  </si>
+  <si>
+    <t>TC_026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ane! oyata kiwwane... </t>
+  </si>
+  <si>
+    <t>අනේ! ඔයාට කිව්වනේ..</t>
+  </si>
+  <si>
+    <t>අනේ! ඔයාට කිව්වනේ...</t>
+  </si>
+  <si>
+    <t>TC_027</t>
+  </si>
+  <si>
+    <t>ගෙදර දොර වහන්න</t>
+  </si>
+  <si>
+    <t>TC_028</t>
+  </si>
+  <si>
+    <t>hinawenna epa 😂</t>
+  </si>
+  <si>
+    <t>හිනා වෙන්න එපා 😂</t>
+  </si>
+  <si>
+    <t>හිනාවෙන්න එපා 😂</t>
+  </si>
+  <si>
+    <t>TC_029</t>
+  </si>
+  <si>
+    <t>අපි breakfast ගත්තා</t>
+  </si>
+  <si>
+    <t>TC_030</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> karunakara seat ekadenna</t>
+  </si>
+  <si>
+    <t>කරුණාකර seat එක දෙන්න</t>
+  </si>
+  <si>
+    <t>කරුණාකර seat එකදෙන්න</t>
+  </si>
+  <si>
+    <t>Command forms</t>
+  </si>
+  <si>
+    <t>Evidence: Input gives an instruction or command.</t>
+  </si>
+  <si>
+    <t>TC_031</t>
+  </si>
+  <si>
+    <t>හරි මම බලන්නම්</t>
+  </si>
+  <si>
+    <t>TC_032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">proj eka iwaraida </t>
+  </si>
+  <si>
+    <t>proj එක ඉවරයිද</t>
+  </si>
+  <si>
+    <t>ප්රොජෙක් එක ඉවරයිද</t>
+  </si>
+  <si>
+    <t>TC_033</t>
+  </si>
+  <si>
+    <t>laptop charger eka ko</t>
+  </si>
+  <si>
+    <t>laptop charger එක කො</t>
+  </si>
+  <si>
+    <t>laptop charger එක කෝ</t>
+  </si>
+  <si>
+    <t>TC_034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">please call me back </t>
+  </si>
+  <si>
+    <t>please නැවත call කරන්න</t>
+  </si>
+  <si>
+    <t>please call me back</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Evidence: Input politely asks for help or action.</t>
+  </si>
+  <si>
+    <t>TC_035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ok mama ennam </t>
+  </si>
+  <si>
+    <t>ඕකේ මම එන්නම්</t>
+  </si>
+  <si>
+    <t>ඕක මම එන්නම්</t>
+  </si>
+  <si>
+    <t>TC_036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lol eka nisa hina una </t>
+  </si>
+  <si>
+    <t>lol එක නිසා හිනා උනා</t>
+  </si>
+  <si>
+    <t>ලොල් එක නිසා හිනා උනා</t>
+  </si>
+  <si>
+    <t>TC_037</t>
+  </si>
+  <si>
+    <t>nidimathii bn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> නිදිමතී බන්</t>
+  </si>
+  <si>
+    <t>නිදිමතයි බන්</t>
+  </si>
+  <si>
+    <t>TC_038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">meeh balapan </t>
+  </si>
+  <si>
+    <t>මේහ් බලපන්</t>
+  </si>
+  <si>
+    <t>මීහ් බලපන්</t>
+  </si>
+  <si>
+    <t>TC_039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">send karanna https://abc.lk </t>
+  </si>
+  <si>
+    <t>send කරන්න https://abc.lk</t>
+  </si>
+  <si>
+    <t>සෙන්ඩ් කරන්න https://abc.ල්ක්</t>
+  </si>
+  <si>
+    <t>Online Identifiers in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: Input includes a URL, email, or online handle.</t>
+  </si>
+  <si>
+    <t>TC_040</t>
+  </si>
+  <si>
+    <t>event eka April 24th</t>
+  </si>
+  <si>
+    <t>event එක April 24 වෙනිදා</t>
+  </si>
+  <si>
+    <t>event එක April 24th</t>
+  </si>
+  <si>
+    <t>TC_041</t>
+  </si>
+  <si>
+    <t>lecture එක ඉවරයි</t>
+  </si>
+  <si>
+    <t>TC_042</t>
+  </si>
+  <si>
+    <t>මේක 12/05/26 ඕනේ</t>
+  </si>
+  <si>
+    <t>TC_043</t>
+  </si>
+  <si>
+    <t>snapchat ekt dapan</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Snapchat එකට දාපන්</t>
+  </si>
+  <si>
+    <t>ස්නාප්චට් එකට දාපන්</t>
+  </si>
+  <si>
+    <t>TC_044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mta stressi 😩	</t>
+  </si>
+  <si>
+    <t>මට stress ඉ      😩</t>
+  </si>
+  <si>
+    <t>මට stressයි</t>
+  </si>
+  <si>
+    <t>TC_045</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ඔක්කොම එල බලමු</t>
+  </si>
+  <si>
+    <t>TC_046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">msg karanna @devini_22 </t>
+  </si>
+  <si>
+    <t>message කරන්න @devini_22</t>
+  </si>
+  <si>
+    <t>msg කරන්න @devini_22</t>
+  </si>
+  <si>
+    <t>TC_047</t>
+  </si>
+  <si>
+    <t>meka harima boring</t>
+  </si>
+  <si>
+    <t>මේක හරිම බෝරිං</t>
+  </si>
+  <si>
+    <t>මේක හරිම බොරින්ග්</t>
+  </si>
+  <si>
+    <t>TC_048</t>
+  </si>
+  <si>
+    <t>8.30 am ta set wemu</t>
+  </si>
+  <si>
+    <t>උදේ 8.30 ට සෙට් වෙමු</t>
+  </si>
+  <si>
+    <t>8.30 ආම් ට set වෙමු</t>
+  </si>
+  <si>
+    <t>TC_049</t>
+  </si>
+  <si>
+    <t>meka user-friendly neda?</t>
+  </si>
+  <si>
+    <t>මේක යූසර් ෆ්‍රෙන්ඩ්ලි නේද?</t>
+  </si>
+  <si>
+    <t>මේක user-friendly නේද?</t>
+  </si>
+  <si>
+    <t>Question forms</t>
+  </si>
+  <si>
+    <t>Evidence: Input is structured as a question.</t>
+  </si>
+  <si>
+    <t>TC_050</t>
+  </si>
+  <si>
+    <t>next mon. hamba wemu</t>
+  </si>
+  <si>
+    <t>ලබන සඳුදා හම්බ වෙමු</t>
+  </si>
+  <si>
+    <t>ඊළඟ මොන්. හම්බ වෙමු</t>
+  </si>
+  <si>
+    <t>bluetooth on kaaarapaan</t>
+  </si>
+  <si>
+    <t>bluetooth on කවරපන්</t>
+  </si>
+  <si>
+    <t>ggeddhaara door eka vahannaa</t>
+  </si>
+  <si>
+    <t>ගෙදර දොර එක වහන්න</t>
+  </si>
+  <si>
+    <t>api breakfast gaathtaaa</t>
+  </si>
+  <si>
+    <t>අපි breakfast ගානට</t>
+  </si>
+  <si>
+    <t>ii mama baalannnmm</t>
+  </si>
+  <si>
+    <t>හරි මම බලලන්නම්</t>
+  </si>
+  <si>
+    <t>lecturre eekkaaaaaa iiwriii</t>
+  </si>
+  <si>
+    <t>lecture එකක ඉවරයි</t>
+  </si>
+  <si>
+    <t>meaka 12/05/26 ooneeeeee</t>
+  </si>
+  <si>
+    <t>මේකා 12/05/26 ඕනේ</t>
+  </si>
+  <si>
+    <t>okkm eela blmuuuu</t>
+  </si>
+  <si>
+    <t>ඔක්කොම එලා බලමු</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="26">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,6 +848,30 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Iskoola Pota"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F2020"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -77,16 +891,87 @@
       <name val="Iskoola Pota"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -96,25 +981,25 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom/>
@@ -122,46 +1007,241 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -219,7 +1299,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -254,7 +1334,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -429,29 +1509,24 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H144"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="49.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="3" max="3" width="22.109375" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.33203125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="7" max="7" width="42.21875" customWidth="1"/>
+    <col min="8" max="8" width="53.6640625" customWidth="1"/>
     <col min="9" max="10" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="36.6" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,86 +1545,1617 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-    </row>
-    <row r="5" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:6" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="G1" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.4" customHeight="1">
+      <c r="A2" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.4" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.4" customHeight="1">
+      <c r="A4" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="22.8" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="22.8" customHeight="1">
+      <c r="A6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.399999999999999" customHeight="1">
+      <c r="A7" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="53" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="20.399999999999999" customHeight="1">
+      <c r="A8" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="25.8" customHeight="1">
+      <c r="A9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="48" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="29.4" customHeight="1" thickBot="1">
+      <c r="A10" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27" customHeight="1">
+      <c r="A11" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="24" customHeight="1">
+      <c r="A12" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="34.799999999999997" customHeight="1">
+      <c r="A13" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="27" customHeight="1">
+      <c r="A14" s="29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="31.2" customHeight="1">
+      <c r="A15" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="F15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="20.399999999999999" customHeight="1">
+      <c r="A16" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F16" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.600000000000001" customHeight="1">
+      <c r="A17" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="31.8" customHeight="1">
+      <c r="A18" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A19" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" t="s">
+        <v>98</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G19" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A20" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" t="s">
+        <v>103</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="H20" s="48" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="49.8" customHeight="1">
+      <c r="A21" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="47.4" customHeight="1">
+      <c r="A22" s="39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B22" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A23" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A24" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D24" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" t="s">
+        <v>124</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="H24" s="48" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A25" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E25" t="s">
+        <v>130</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A26" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="E26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="H26" s="48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A27" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A28" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" t="s">
+        <v>146</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H28" s="48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A29" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>241</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A30" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="H30" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A31" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>243</v>
+      </c>
+      <c r="D31" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>244</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H31" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A32" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" t="s">
+        <v>158</v>
+      </c>
+      <c r="F32" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32" s="48" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A33" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" t="s">
+        <v>162</v>
+      </c>
+      <c r="E33" s="52" t="s">
+        <v>246</v>
+      </c>
+      <c r="F33" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A34" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" t="s">
+        <v>165</v>
+      </c>
+      <c r="E34" t="s">
+        <v>166</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A35" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" t="s">
+        <v>169</v>
+      </c>
+      <c r="E35" t="s">
+        <v>170</v>
+      </c>
+      <c r="F35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="48" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A36" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" t="s">
+        <v>174</v>
+      </c>
+      <c r="F36" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="H36" s="48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A37" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="D37" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" t="s">
+        <v>180</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="H37" s="48" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A38" s="39" t="s">
+        <v>181</v>
+      </c>
+      <c r="B38" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C38" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="D38" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" t="s">
+        <v>184</v>
+      </c>
+      <c r="F38" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="H38" s="48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A39" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="B39" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="45" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="H39" s="48" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A40" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" t="s">
+        <v>191</v>
+      </c>
+      <c r="E40" t="s">
+        <v>192</v>
+      </c>
+      <c r="F40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G40" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H40" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A41" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C41" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="E41" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" t="s">
+        <v>13</v>
+      </c>
+      <c r="G41" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="H41" s="48" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A42" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" t="s">
+        <v>202</v>
+      </c>
+      <c r="F42" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G42" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="H42" s="48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A43" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" s="52" t="s">
+        <v>247</v>
+      </c>
+      <c r="D43" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" s="52" t="s">
+        <v>248</v>
+      </c>
+      <c r="F43" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G43" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A44" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" s="52" t="s">
+        <v>249</v>
+      </c>
+      <c r="D44" t="s">
+        <v>206</v>
+      </c>
+      <c r="E44" s="52" t="s">
+        <v>250</v>
+      </c>
+      <c r="F44" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="H44" s="48" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A45" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>208</v>
+      </c>
+      <c r="D45" t="s">
+        <v>209</v>
+      </c>
+      <c r="E45" t="s">
+        <v>210</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="G45" s="48" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A46" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="B46" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>212</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G46" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="H46" s="48" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A47" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C47" s="52" t="s">
+        <v>251</v>
+      </c>
+      <c r="D47" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="E47" s="52" t="s">
+        <v>252</v>
+      </c>
+      <c r="F47" s="52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G47" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A48" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="B48" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="D48" t="s">
+        <v>219</v>
+      </c>
+      <c r="E48" t="s">
+        <v>220</v>
+      </c>
+      <c r="F48" t="s">
+        <v>13</v>
+      </c>
+      <c r="G48" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="48" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A49" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" t="s">
+        <v>224</v>
+      </c>
+      <c r="F49" t="s">
+        <v>13</v>
+      </c>
+      <c r="G49" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A50" s="39" t="s">
+        <v>225</v>
+      </c>
+      <c r="B50" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="D50" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="E50" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" t="s">
+        <v>13</v>
+      </c>
+      <c r="G50" s="48" t="s">
+        <v>110</v>
+      </c>
+      <c r="H50" s="48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A51" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C51" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="D51" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="E51" t="s">
+        <v>232</v>
+      </c>
+      <c r="F51" t="s">
+        <v>13</v>
+      </c>
+      <c r="G51" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="H51" s="48" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A52" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B52" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="C52" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" s="46" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" t="s">
+        <v>238</v>
+      </c>
+      <c r="F52" t="s">
+        <v>13</v>
+      </c>
+      <c r="G52" s="48" t="s">
+        <v>44</v>
+      </c>
+      <c r="H52" s="48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A53" s="39"/>
+    </row>
+    <row r="54" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A54" s="39"/>
+    </row>
+    <row r="55" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A55" s="39"/>
+    </row>
+    <row r="56" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A56" s="39"/>
+    </row>
+    <row r="57" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A57" s="39"/>
+    </row>
+    <row r="58" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A58" s="39"/>
+    </row>
+    <row r="59" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A59" s="39"/>
+    </row>
+    <row r="60" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A60" s="39"/>
+    </row>
+    <row r="61" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A61" s="39"/>
+    </row>
+    <row r="62" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A62" s="39"/>
+    </row>
+    <row r="63" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A63" s="39"/>
+    </row>
+    <row r="64" spans="1:8" ht="49.95" customHeight="1">
+      <c r="A64" s="39"/>
+    </row>
+    <row r="65" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A65" s="39"/>
+    </row>
+    <row r="66" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A66" s="39"/>
+    </row>
+    <row r="67" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A67" s="39"/>
+    </row>
+    <row r="68" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A68" s="39"/>
+    </row>
+    <row r="69" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A69" s="39"/>
+    </row>
+    <row r="70" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A70" s="39"/>
+    </row>
+    <row r="71" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A71" s="39"/>
+    </row>
+    <row r="72" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A72" s="39"/>
+    </row>
+    <row r="73" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A73" s="39"/>
+    </row>
+    <row r="74" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A74" s="39"/>
+    </row>
+    <row r="75" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A75" s="39"/>
+    </row>
+    <row r="76" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A76" s="39"/>
+    </row>
+    <row r="77" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A77" s="39"/>
+    </row>
+    <row r="78" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A78" s="39"/>
+    </row>
+    <row r="79" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A79" s="39"/>
+    </row>
+    <row r="80" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A80" s="39"/>
+    </row>
+    <row r="81" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A81" s="39"/>
+    </row>
+    <row r="82" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A82" s="39"/>
+    </row>
+    <row r="83" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A83" s="39"/>
+    </row>
+    <row r="84" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A84" s="39"/>
+    </row>
+    <row r="85" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A85" s="39"/>
+    </row>
+    <row r="86" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A86" s="39"/>
+    </row>
+    <row r="87" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A87" s="39"/>
+    </row>
+    <row r="88" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A88" s="39"/>
+    </row>
+    <row r="89" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A89" s="39"/>
+    </row>
+    <row r="90" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A90" s="39"/>
+    </row>
+    <row r="91" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A91" s="39"/>
+    </row>
+    <row r="92" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A92" s="39"/>
+    </row>
+    <row r="93" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A93" s="39"/>
+    </row>
+    <row r="94" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A94" s="39"/>
+    </row>
+    <row r="95" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A95" s="39"/>
+    </row>
+    <row r="96" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A96" s="39"/>
+    </row>
+    <row r="97" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A97" s="39"/>
+    </row>
+    <row r="98" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A98" s="39"/>
+    </row>
+    <row r="99" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A99" s="39"/>
+    </row>
+    <row r="100" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A100" s="39"/>
+    </row>
+    <row r="101" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A101" s="39"/>
+    </row>
+    <row r="102" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A102" s="39"/>
+    </row>
+    <row r="103" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A103" s="39"/>
+    </row>
+    <row r="104" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A104" s="39"/>
+    </row>
+    <row r="105" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A105" s="39"/>
+    </row>
+    <row r="106" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A106" s="39"/>
+    </row>
+    <row r="107" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A107" s="39"/>
+    </row>
+    <row r="108" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A108" s="39"/>
+    </row>
+    <row r="109" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A109" s="39"/>
+    </row>
+    <row r="110" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A110" s="39"/>
+    </row>
+    <row r="111" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A111" s="39"/>
+    </row>
+    <row r="112" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A112" s="39"/>
+    </row>
+    <row r="113" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A113" s="39"/>
+    </row>
+    <row r="114" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A114" s="39"/>
+    </row>
+    <row r="115" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A115" s="39"/>
+    </row>
+    <row r="116" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A116" s="39"/>
+    </row>
+    <row r="117" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A117" s="39"/>
+    </row>
+    <row r="118" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A118" s="39"/>
+    </row>
+    <row r="119" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A119" s="39"/>
+    </row>
+    <row r="120" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A120" s="39"/>
+    </row>
+    <row r="121" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A121" s="39"/>
+    </row>
+    <row r="122" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A122" s="39"/>
+    </row>
+    <row r="123" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A123" s="39"/>
+    </row>
+    <row r="124" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A124" s="39"/>
+    </row>
+    <row r="125" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A125" s="39"/>
+    </row>
+    <row r="126" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A126" s="39"/>
+    </row>
+    <row r="127" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A127" s="39"/>
+    </row>
+    <row r="128" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A128" s="39"/>
+    </row>
+    <row r="129" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A129" s="39"/>
+    </row>
+    <row r="130" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A130" s="39"/>
+    </row>
+    <row r="131" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A131" s="39"/>
+    </row>
+    <row r="132" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A132" s="39"/>
+    </row>
+    <row r="133" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A133" s="39"/>
+    </row>
+    <row r="134" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A134" s="39"/>
+    </row>
+    <row r="135" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A135" s="39"/>
+    </row>
+    <row r="136" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A136" s="39"/>
+    </row>
+    <row r="137" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A137" s="39"/>
+    </row>
+    <row r="138" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A138" s="39"/>
+    </row>
+    <row r="139" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A139" s="39"/>
+    </row>
+    <row r="140" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A140" s="39"/>
+    </row>
+    <row r="141" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A141" s="39"/>
+    </row>
+    <row r="142" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A142" s="39"/>
+    </row>
+    <row r="143" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A143" s="39"/>
+    </row>
+    <row r="144" spans="1:1" ht="49.95" customHeight="1">
+      <c r="A144" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D2:D5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
 </worksheet>
 </file>